--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T15:49:35+00:00</t>
+    <t>2026-01-30T11:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T11:01:37+00:00</t>
+    <t>2026-01-30T14:32:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Responsable et auteur du statut de l'évaluation</t>
+    <t>TDDUI QR Participant</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T14:32:15+00:00</t>
+    <t>2026-02-09T09:12:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -374,7 +374,7 @@
     <t>Extension.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner)
 </t>
   </si>
   <si>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T09:12:46+00:00</t>
+    <t>2026-02-10T10:23:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:23:53+00:00</t>
+    <t>2026-02-11T15:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:25:25+00:00</t>
+    <t>2026-02-16T10:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:19:26+00:00</t>
+    <t>2026-02-23T14:19:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T14:19:51+00:00</t>
+    <t>2026-02-24T10:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-qr-participant.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="131">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:04:30+00:00</t>
+    <t>2026-02-26T15:31:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Extension permettant d'ajouter le responsable de l'évaluation et l'auteur du statut de l'évaluation dans un QuestionnaireResponse.</t>
+    <t>Extension permettant d'ajouter le responsable et le porteur de l'évaluation dans un QuestionnaireResponse.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -391,25 +391,29 @@
 </t>
   </si>
   <si>
-    <t>Extension.extension:TDDUIStatusAuthor</t>
-  </si>
-  <si>
-    <t>TDDUIStatusAuthor</t>
-  </si>
-  <si>
-    <t>Auteur du statut de l'évaluation.</t>
-  </si>
-  <si>
-    <t>Extension.extension:TDDUIStatusAuthor.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:TDDUIStatusAuthor.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:TDDUIStatusAuthor.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:TDDUIStatusAuthor.value[x]</t>
+    <t>Extension.extension:TDDUIHolder</t>
+  </si>
+  <si>
+    <t>TDDUIHolder</t>
+  </si>
+  <si>
+    <t>Personne morale porteuse de l'évaluation de l'usager.</t>
+  </si>
+  <si>
+    <t>Extension.extension:TDDUIHolder.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:TDDUIHolder.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:TDDUIHolder.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:TDDUIHolder.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
+</t>
   </si>
   <si>
     <t>base64Binary
@@ -726,9 +730,9 @@
   <dimension ref="A1:AK16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.81640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.00390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="24.9921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="15.37890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2151,7 +2155,7 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>118</v>
@@ -2359,7 +2363,7 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>118</v>
